--- a/data/output_v2/backtest_results.xlsx
+++ b/data/output_v2/backtest_results.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,12 +506,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>中证2000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>518880.SH</t>
+          <t>563300.SH</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -524,7 +524,7 @@
         <v>46035</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>327.8</v>
+        <v>3248</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -535,12 +535,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>159980.SZ</t>
+          <t>518880.SH</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -553,7 +553,7 @@
         <v>46035</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1376</v>
+        <v>327.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -564,12 +564,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>中证2000</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>563300.SH</t>
+          <t>159980.SZ</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -582,7 +582,7 @@
         <v>46035</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3248</v>
+        <v>1376</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>亚太精选</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518880.SH</t>
+          <t>159687.SZ</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -756,7 +756,7 @@
         <v>46055</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-880.8</v>
+        <v>-3810.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -767,12 +767,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>亚太精选</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>159687.SZ</t>
+          <t>518880.SH</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -785,7 +785,7 @@
         <v>46055</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-3810.6</v>
+        <v>-880.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -854,12 +854,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>中证2000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>563300.SH</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -872,7 +872,7 @@
         <v>46057</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>12.8</v>
+        <v>1786</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>中证2000</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>563300.SH</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -930,7 +930,7 @@
         <v>46057</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1786</v>
+        <v>12.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -999,12 +999,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>中证2000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>563300.SH</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1017,7 +1017,7 @@
         <v>46064</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>27.5</v>
+        <v>880.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>中证2000</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>563300.SH</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1046,7 +1046,7 @@
         <v>46064</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>880.1</v>
+        <v>27.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1057,12 +1057,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>亚太精选</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159687.SZ</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1075,7 +1075,7 @@
         <v>46083</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>27</v>
+        <v>-892.8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1086,12 +1086,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>亚太精选</t>
+          <t>中证2000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>159687.SZ</t>
+          <t>563300.SH</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1104,7 +1104,7 @@
         <v>46083</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-892.8</v>
+        <v>1524.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1115,12 +1115,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>中证2000</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>563300.SH</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1133,7 +1133,7 @@
         <v>46083</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1524.6</v>
+        <v>27</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1202,12 +1202,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>豆粕</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159985.SZ</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1220,7 +1220,7 @@
         <v>46084</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.2</v>
+        <v>567.8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1231,12 +1231,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>豆粕</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>159985.SZ</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1249,7 +1249,7 @@
         <v>46084</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>567.8</v>
+        <v>4.2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1318,25 +1318,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>能源化工</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159981.SZ</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>22.8</v>
+        <v>6615</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>能源化工</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>159981.SZ</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46091</v>
+        <v>46084</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>6615</v>
+        <v>22.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1492,12 +1492,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>能源化工</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159981.SZ</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1510,7 +1510,7 @@
         <v>46119</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>73.5</v>
+        <v>4502.1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1521,12 +1521,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>能源化工</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>159981.SZ</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1539,7 +1539,7 @@
         <v>46119</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>4502.1</v>
+        <v>73.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1579,25 +1579,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>科创创业</t>
+          <t>能源化工</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>159781.SZ</t>
+          <t>159981.SZ</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>46122</v>
+        <v>46119</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>5076.4</v>
+        <v>-3044.4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>能源化工</t>
+          <t>科创创业</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>159981.SZ</t>
+          <t>159781.SZ</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-3044.4</v>
+        <v>5076.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1724,25 +1724,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>科创创业</t>
+          <t>纳指</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>159781.SZ</t>
+          <t>159941.SZ</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>15441.3</v>
+        <v>2032</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>纳指</t>
+          <t>科创创业</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>159941.SZ</t>
+          <t>159781.SZ</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>46139</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2032</v>
+        <v>15441.3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>纳指</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159941.SZ</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>46119</v>
+        <v>46156</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-100</v>
+        <v>1538.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1811,25 +1811,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>纳指</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>159941.SZ</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>46156</v>
+        <v>46119</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1538.7</v>
+        <v>-100</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>科创创业</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159781.SZ</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>46170</v>
+        <v>46205</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>-856</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2130,12 +2130,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>科创创业</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>159781.SZ</t>
+          <t>512010.SH</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2148,7 +2148,7 @@
         <v>46211</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>-856</v>
+        <v>-1923.2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2159,25 +2159,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>512010.SH</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>46205</v>
+        <v>46170</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>-1923.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2826,12 +2826,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>纳指</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159941.SZ</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2844,7 +2844,7 @@
         <v>46289</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>12</v>
+        <v>-172.2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2884,12 +2884,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>纳指</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>159941.SZ</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2902,7 +2902,7 @@
         <v>46289</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>-172.2</v>
+        <v>12</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>国开债券</t>
+          <t>纳指</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>159650.SZ</t>
+          <t>159941.SZ</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2931,7 +2931,7 @@
         <v>46310</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>62.4</v>
+        <v>92.8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2971,12 +2971,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>纳指</t>
+          <t>国开债券</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>159941.SZ</t>
+          <t>159650.SZ</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2989,7 +2989,7 @@
         <v>46310</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>92.8</v>
+        <v>62.4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3052,6 +3052,35 @@
       <c r="G90" t="inlineStr">
         <is>
           <t>切换仓位</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>纳指</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>159941.SZ</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>-758.5</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>止损</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V192"/>
+  <dimension ref="A1:V193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16167,6 +16196,74 @@
       </c>
       <c r="V192" s="3" t="n">
         <v>239677</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>54135</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>31789.8</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" s="3" t="n">
+        <v>115124.2</v>
+      </c>
+      <c r="Q193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" s="3" t="n">
+        <v>38204.9</v>
+      </c>
+      <c r="V193" s="3" t="n">
+        <v>239253.9</v>
       </c>
     </row>
   </sheetData>
@@ -16180,7 +16277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T192"/>
+  <dimension ref="A1:T193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28127,6 +28224,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v>18900</v>
+      </c>
+      <c r="K193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" s="4" t="n">
+        <v>133400</v>
+      </c>
+      <c r="Q193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
